--- a/analysis/cocoblu-supply-2026-09-04/Cocoblu_Supply_Plan_v3_ISK3.xlsx
+++ b/analysis/cocoblu-supply-2026-09-04/Cocoblu_Supply_Plan_v3_ISK3.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'0_Summary'!$A$1:$B$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_Dispatch by PO'!$A$1:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_Dispatch lines'!$A$1:$N$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_Dispatch lines'!$A$1:$N$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3_SKU plan 35d'!$A$1:$S$109</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4_Franchise cap'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5_Ask Amazon for PO'!$A$1:$K$7</definedName>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4221</v>
+        <v>4281</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7439495</v>
+        <v>7469978</v>
       </c>
     </row>
     <row r="9">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9679</v>
+        <v>9619</v>
       </c>
     </row>
     <row r="10">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -695,10 +695,10 @@
         <v>46285</v>
       </c>
       <c r="E2" t="n">
-        <v>1566</v>
+        <v>1626</v>
       </c>
       <c r="F2" t="n">
-        <v>3206813</v>
+        <v>3237296</v>
       </c>
     </row>
     <row r="3">
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2397,50 +2397,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>39VRVKCF</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0DPHR4FG7</t>
+          <t>B0D8443PTW</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PBLUCIDWHT</t>
+          <t>QUADPROMAXBLK</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stuffcool Lucid 15W Smallest Magnetic Wireless Powerbank 5000Mah Battery Capacity for iPhone 16</t>
+          <t>Stuffcool Quad Pro Max 4 in 1 Metal Braided Cable 1.5m 240W Rugged e-Marker chip gold plated co</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>942.96</v>
+        <v>508.05</v>
       </c>
       <c r="G29" t="n">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="H29" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>46266</v>
+        <v>46285</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>46270</v>
+        <v>46289</v>
       </c>
       <c r="M29" t="n">
-        <v>28289</v>
+        <v>30483</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2459,30 +2459,30 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0FT2VNW5H</t>
+          <t>B0DPHR4FG7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>WCZENO30WWHT</t>
+          <t>PBLUCIDWHT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stuffcool Zeno 30W GaN Type C Fast Charger Retractable Cable 75cm PD PPS iPhone Pixel Samsung S</t>
+          <t>Stuffcool Lucid 15W Smallest Magnetic Wireless Powerbank 5000Mah Battery Capacity for iPhone 16</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1084.2</v>
+        <v>942.96</v>
       </c>
       <c r="G30" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H30" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>46237</v>
@@ -2494,7 +2494,7 @@
         <v>46270</v>
       </c>
       <c r="M30" t="n">
-        <v>24937</v>
+        <v>28289</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2505,50 +2505,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>39VRVKCF</t>
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0FSSCW7WZ</t>
+          <t>B0FT2VNW5H</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DUPLOBLK</t>
+          <t>WCZENO30WWHT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided Dual USB-C Connectors with Smart E-Ma</t>
+          <t>Stuffcool Zeno 30W GaN Type C Fast Charger Retractable Cable 75cm PD PPS iPhone Pixel Samsung S</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>698.6900000000001</v>
+        <v>1084.2</v>
       </c>
       <c r="G31" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="H31" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>46285</v>
+        <v>46266</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>46289</v>
+        <v>46270</v>
       </c>
       <c r="M31" t="n">
-        <v>24454</v>
+        <v>24937</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2559,50 +2559,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0FT2VNW5H</t>
+          <t>B0FSSCW7WZ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>WCZENO30WWHT</t>
+          <t>DUPLOBLK</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Stuffcool Zeno 30W GaN Type C Fast Charger Retractable Cable 75cm PD PPS iPhone Pixel Samsung S</t>
+          <t>Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided Dual USB-C Connectors with Smart E-Ma</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1084.2</v>
+        <v>698.6900000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="H32" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="I32" t="n">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>46266</v>
+        <v>46244</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>46294</v>
+        <v>46285</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>46298</v>
+        <v>46289</v>
       </c>
       <c r="M32" t="n">
-        <v>22768</v>
+        <v>24454</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2613,50 +2613,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0H5HYK4KZ</t>
+          <t>B0FT2VNW5H</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PBOMNIIVRY</t>
+          <t>WCZENO30WWHT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank with Dedicated Apple Watch Charging </t>
+          <t>Stuffcool Zeno 30W GaN Type C Fast Charger Retractable Cable 75cm PD PPS iPhone Pixel Samsung S</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1692.59</v>
+        <v>1084.2</v>
       </c>
       <c r="G33" t="n">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="H33" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I33" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>46258</v>
+        <v>46266</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>46286</v>
+        <v>46294</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>46290</v>
+        <v>46298</v>
       </c>
       <c r="M33" t="n">
-        <v>20311</v>
+        <v>22768</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2667,50 +2667,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>39VRVKCF</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0H6J3YQ1D</t>
+          <t>B0H5HYK4KZ</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>WCNVS25CBLU</t>
+          <t>PBOMNIIVRY</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pixel &amp; iPhone Blue</t>
+          <t xml:space="preserve">Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank with Dedicated Apple Watch Charging </t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>433.36</v>
+        <v>1692.59</v>
       </c>
       <c r="G34" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H34" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>46266</v>
+        <v>46286</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>46270</v>
+        <v>46290</v>
       </c>
       <c r="M34" t="n">
-        <v>19935</v>
+        <v>20311</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2721,50 +2721,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>39VRVKCF</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0FV2VNK12</t>
+          <t>B0H6J3YQ1D</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>WCEMP75SIL</t>
+          <t>WCNVS25CBLU</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pixel &amp; iPhone Blue</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2168.95</v>
+        <v>433.36</v>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="H35" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>46285</v>
+        <v>46266</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>46289</v>
+        <v>46270</v>
       </c>
       <c r="M35" t="n">
-        <v>19521</v>
+        <v>19935</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2775,50 +2775,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0FTFVKTH6</t>
+          <t>B0FV2VNK12</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ULTIMUS128BLK</t>
+          <t>WCEMP75SIL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stuffcool Ultimus 128W Super Fast Car Charger Dual Type-C USB-A PD 65W PD 30W QC 30W Compatible</t>
+          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1518.1</v>
+        <v>2168.95</v>
       </c>
       <c r="G36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>46279</v>
+        <v>46285</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="M36" t="n">
-        <v>16699</v>
+        <v>19521</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2829,50 +2829,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0FV2VNK12</t>
+          <t>B0FTFVKTH6</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>WCEMP75SIL</t>
+          <t>ULTIMUS128BLK</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
+          <t>Stuffcool Ultimus 128W Super Fast Car Charger Dual Type-C USB-A PD 65W PD 30W QC 30W Compatible</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2168.95</v>
+        <v>1518.1</v>
       </c>
       <c r="G37" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I37" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>46266</v>
+        <v>46251</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>46294</v>
+        <v>46279</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>46298</v>
+        <v>46283</v>
       </c>
       <c r="M37" t="n">
-        <v>13014</v>
+        <v>16699</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2883,50 +2883,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>39VRVKCF</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>46237</v>
+        <v>46265</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DZHKBBM1</t>
+          <t>B0FV2VNK12</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PBMAVERICKBLK</t>
+          <t>WCEMP75SIL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Maverick Mini 20,000mAh Powerbank with 20W Built-in Lightning &amp; Type-C Cables, 22.5W </t>
+          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1219.73</v>
+        <v>2168.95</v>
       </c>
       <c r="G38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>46237</v>
+        <v>46266</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>46266</v>
+        <v>46294</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>46270</v>
+        <v>46298</v>
       </c>
       <c r="M38" t="n">
-        <v>12197</v>
+        <v>13014</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -2937,50 +2937,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>39VRVKCF</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0D3N594JW</t>
+          <t>B0DZHKBBM1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>WRLREVELBLK</t>
+          <t>PBMAVERICKBLK</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stuffcool Revel Magnetic Wireless Qi2 Certified Charger- Charges iPhone 12/13/14/15/16 and Andr</t>
+          <t xml:space="preserve">Stuffcool Maverick Mini 20,000mAh Powerbank with 20W Built-in Lightning &amp; Type-C Cables, 22.5W </t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>762.2</v>
+        <v>1219.73</v>
       </c>
       <c r="G39" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H39" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="3" t="n">
+        <v>46237</v>
+      </c>
+      <c r="K39" s="3" t="n">
         <v>46266</v>
       </c>
-      <c r="K39" s="3" t="n">
-        <v>46294</v>
-      </c>
       <c r="L39" s="3" t="n">
-        <v>46298</v>
+        <v>46270</v>
       </c>
       <c r="M39" t="n">
-        <v>12195</v>
+        <v>12197</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -2991,50 +2991,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0FTFVKTH6</t>
+          <t>B0D3N594JW</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ULTIMUS128BLK</t>
+          <t>WRLREVELBLK</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stuffcool Ultimus 128W Super Fast Car Charger Dual Type-C USB-A PD 65W PD 30W QC 30W Compatible</t>
+          <t>Stuffcool Revel Magnetic Wireless Qi2 Certified Charger- Charges iPhone 12/13/14/15/16 and Andr</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1518.1</v>
+        <v>762.2</v>
       </c>
       <c r="G40" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H40" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>46258</v>
+        <v>46266</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>46286</v>
+        <v>46294</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>46290</v>
+        <v>46298</v>
       </c>
       <c r="M40" t="n">
-        <v>12145</v>
+        <v>12195</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -3045,50 +3045,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6WAHMIEG</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>46252</v>
+        <v>46258</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CCJ8BX6C</t>
+          <t>B0FTFVKTH6</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PBCLICKGRY</t>
+          <t>ULTIMUS128BLK</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stuffcool Click 5000mAh Made in India Magnetic Wireless Powerbank with 18W PD Fast Charing Type</t>
+          <t>Stuffcool Ultimus 128W Super Fast Car Charger Dual Type-C USB-A PD 65W PD 30W QC 30W Compatible</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1185.85</v>
+        <v>1518.1</v>
       </c>
       <c r="G41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>46278</v>
+        <v>46258</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="M41" t="n">
-        <v>11858</v>
+        <v>12145</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -3099,50 +3099,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>6WAHMIEG</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>46258</v>
+        <v>46252</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0FV2VNK12</t>
+          <t>B0CCJ8BX6C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>WCEMP75SIL</t>
+          <t>PBCLICKGRY</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
+          <t>Stuffcool Click 5000mAh Made in India Magnetic Wireless Powerbank with 18W PD Fast Charing Type</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2168.95</v>
+        <v>1185.85</v>
       </c>
       <c r="G42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>46258</v>
+        <v>46278</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="M42" t="n">
-        <v>10845</v>
+        <v>11858</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -3153,50 +3153,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0BXXMZLDY</t>
+          <t>B0FV2VNK12</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PBSP85WBLK</t>
+          <t>WCEMP75SIL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stuffcool Super Power 85W 20000mAh Powerbank Compatible to Charge Macbooks, Laptops, iPads, Tab</t>
+          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2960.17</v>
+        <v>2168.95</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>46266</v>
+        <v>46258</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>46298</v>
+        <v>46290</v>
       </c>
       <c r="M43" t="n">
-        <v>5920</v>
+        <v>10845</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -3207,50 +3207,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0H2VFTQ1C</t>
+          <t>B0BXXMZLDY</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>WCNUMEN45PROWHT</t>
+          <t>PBSP85WBLK</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD PPS Fast Charging, Supports Samsung </t>
+          <t>Stuffcool Super Power 85W 20000mAh Powerbank Compatible to Charge Macbooks, Laptops, iPads, Tab</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>867.25</v>
+        <v>2960.17</v>
       </c>
       <c r="G44" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>46251</v>
+        <v>46266</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>46279</v>
+        <v>46294</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>46283</v>
+        <v>46298</v>
       </c>
       <c r="M44" t="n">
-        <v>5204</v>
+        <v>5920</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -3261,50 +3261,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>39VRVKCF</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0GZVCYSXL</t>
+          <t>B0H2VFTQ1C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>WCNVS25CWHT</t>
+          <t>WCNUMEN45PROWHT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pixel &amp; iPhone</t>
+          <t xml:space="preserve">Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD PPS Fast Charging, Supports Samsung </t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>433.36</v>
+        <v>867.25</v>
       </c>
       <c r="G45" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H45" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>46266</v>
+        <v>46279</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>46270</v>
+        <v>46283</v>
       </c>
       <c r="M45" t="n">
-        <v>3467</v>
+        <v>5204</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -3315,50 +3315,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>39VRVKCF</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0DFYZWRFQ</t>
+          <t>B0GZVCYSXL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PBROAM20WHT</t>
+          <t>WCNVS25CWHT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pixel &amp; iPhone</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1067.2</v>
+        <v>433.36</v>
       </c>
       <c r="G46" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>46285</v>
+        <v>46266</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>46289</v>
+        <v>46270</v>
       </c>
       <c r="M46" t="n">
-        <v>3202</v>
+        <v>3467</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -3369,50 +3369,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0DMVN35V5</t>
+          <t>B0DFYZWRFQ</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>RMSIP16PLBLK</t>
+          <t>PBROAM20WHT</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stuffcool Rims Silicone case for iPhone 16 Plus, Magsafe Enabled with a Raised Metallic Frame f</t>
+          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>863.9</v>
+        <v>1067.2</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>46266</v>
+        <v>46244</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>46294</v>
+        <v>46285</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>46298</v>
+        <v>46289</v>
       </c>
       <c r="M47" t="n">
-        <v>1728</v>
+        <v>3202</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -3423,50 +3423,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B0DB1MXGD4</t>
+          <t>B0DMVN35V5</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PBCLICKMAXWHT</t>
+          <t>RMSIP16PLBLK</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Click Max 10000mAh Powerbank with Built-in PD20W Type-C Cable to Fast Charge iPhones </t>
+          <t>Stuffcool Rims Silicone case for iPhone 16 Plus, Magsafe Enabled with a Raised Metallic Frame f</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1363.81</v>
+        <v>863.9</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>46258</v>
+        <v>46266</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>46286</v>
+        <v>46294</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>46290</v>
+        <v>46298</v>
       </c>
       <c r="M48" t="n">
-        <v>1364</v>
+        <v>1728</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -3477,29 +3477,29 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>39VRVKCF</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>B0DDTL6R6Y</t>
+          <t>B0DB1MXGD4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PBMEGAII30WGRN</t>
+          <t>PBCLICKMAXWHT</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stuffcool Mega II Compact 10,000mAh 25W Powerbank with Samsung Super Fast Charging, Charges iPh</t>
+          <t xml:space="preserve">Stuffcool Click Max 10000mAh Powerbank with Built-in PD20W Type-C Cable to Fast Charge iPhones </t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>889.24</v>
+        <v>1363.81</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -3511,16 +3511,16 @@
         <v>0</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>46266</v>
+        <v>46286</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>46270</v>
+        <v>46290</v>
       </c>
       <c r="M49" t="n">
-        <v>889</v>
+        <v>1364</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -3531,50 +3531,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>39VRVKCF</t>
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B0GZVCYSXL</t>
+          <t>B0DDTL6R6Y</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>WCNVS25CWHT</t>
+          <t>PBMEGAII30WGRN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pixel &amp; iPhone</t>
+          <t>Stuffcool Mega II Compact 10,000mAh 25W Powerbank with Samsung Super Fast Charging, Charges iPh</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>433.36</v>
+        <v>889.24</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>46285</v>
+        <v>46266</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>46289</v>
+        <v>46270</v>
       </c>
       <c r="M50" t="n">
-        <v>867</v>
+        <v>889</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -3585,59 +3585,113 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>5OF8HBIC</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>B0GZVCYSXL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>WCNVS25CWHT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pixel &amp; iPhone</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>433.36</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>46244</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="M51" t="n">
+        <v>867</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>P1-Incumbent (running down)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>39VRVKCF</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B52" s="3" t="n">
         <v>46237</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>B0C7QBPS1H</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>QUADN1BLK</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t xml:space="preserve">Stuffcool Quad 4 in 1 Cable 65W PD USB to Lightning, USB to Type-C, Type-C to Lightning &amp; Type </t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="F52" t="n">
         <v>296.19</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G52" t="n">
         <v>1</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H52" t="n">
         <v>1</v>
       </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="n">
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="n">
         <v>46237</v>
       </c>
-      <c r="K51" s="3" t="n">
+      <c r="K52" s="3" t="n">
         <v>46266</v>
       </c>
-      <c r="L51" s="3" t="n">
+      <c r="L52" s="3" t="n">
         <v>46270</v>
       </c>
-      <c r="M51" t="n">
+      <c r="M52" t="n">
         <v>296</v>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>P1-Incumbent (running down)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N51"/>
+  <autoFilter ref="A1:N52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5271,17 +5325,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B0FTFVKTH6</t>
+          <t>B0D8443PTW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ULTIMUS128BLK</t>
+          <t>QUADPROMAXBLK</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Ultimus 128W Super Fast Car Charger Dual Type-C </t>
+          <t>Stuffcool Quad Pro Max 4 in 1 Metal Braided Cable 1.5m 240</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5290,41 +5344,41 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>33</v>
+        <v>360</v>
       </c>
       <c r="H25" t="n">
-        <v>1.666666666666667</v>
+        <v>12</v>
       </c>
       <c r="I25" t="n">
-        <v>19.8</v>
+        <v>30</v>
       </c>
       <c r="J25" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="K25" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="L25" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="M25" t="n">
-        <v>31.2</v>
+        <v>35</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1518.1</v>
+        <v>508.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>28844</v>
+        <v>30483</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>53SMQFHQ, 8Z6APQQC</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="S25" t="b">
@@ -5334,17 +5388,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B0DPHR4FG7</t>
+          <t>B0FTFVKTH6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PBLUCIDWHT</t>
+          <t>ULTIMUS128BLK</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Stuffcool Lucid 15W Smallest Magnetic Wireless Powerbank 5</t>
+          <t xml:space="preserve">Stuffcool Ultimus 128W Super Fast Car Charger Dual Type-C </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5353,40 +5407,41 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>1.666666666666667</v>
+      </c>
+      <c r="I26" t="n">
+        <v>19.8</v>
       </c>
       <c r="J26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K26" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="L26" t="n">
-        <v>30</v>
+        <v>19</v>
+      </c>
+      <c r="M26" t="n">
+        <v>31.2</v>
       </c>
       <c r="N26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>942.96</v>
+        <v>1518.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>28289</v>
+        <v>28844</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>39VRVKCF</t>
+          <t>53SMQFHQ, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S26" t="b">
@@ -5396,17 +5451,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B0FSSCW7WZ</t>
+          <t>B0DPHR4FG7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DUPLOBLK</t>
+          <t>PBLUCIDWHT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided </t>
+          <t>Stuffcool Lucid 15W Smallest Magnetic Wireless Powerbank 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5415,41 +5470,40 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>30</v>
+      </c>
+      <c r="K27" t="n">
+        <v>39</v>
+      </c>
+      <c r="L27" t="n">
+        <v>30</v>
+      </c>
+      <c r="N27" t="n">
         <v>9</v>
       </c>
-      <c r="J27" t="n">
-        <v>35</v>
-      </c>
-      <c r="K27" t="n">
-        <v>79</v>
-      </c>
-      <c r="L27" t="n">
-        <v>35</v>
-      </c>
-      <c r="M27" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>44</v>
-      </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>698.6900000000001</v>
+        <v>942.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>24454</v>
+        <v>28289</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>53SMQFHQ, 5OF8HBIC</t>
+          <t>39VRVKCF</t>
         </is>
       </c>
       <c r="S27" t="b">
@@ -5459,17 +5513,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B0H5HYK4KZ</t>
+          <t>B0FSSCW7WZ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PBOMNIIVRY</t>
+          <t>DUPLOBLK</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank</t>
+          <t xml:space="preserve">Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5478,41 +5532,41 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="H28" t="n">
-        <v>2.666666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="I28" t="n">
-        <v>30.375</v>
+        <v>9</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="K28" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L28" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="M28" t="n">
-        <v>34.9</v>
+        <v>35.2</v>
       </c>
       <c r="N28" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1692.59</v>
+        <v>698.6900000000001</v>
       </c>
       <c r="Q28" t="n">
-        <v>20311</v>
+        <v>24454</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>5FPANY5G, 8Z6APQQC</t>
+          <t>53SMQFHQ, 5OF8HBIC</t>
         </is>
       </c>
       <c r="S28" t="b">
@@ -5522,17 +5576,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B0H6J3YQ1D</t>
+          <t>B0H5HYK4KZ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WCNVS25CBLU</t>
+          <t>PBOMNIIVRY</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pi</t>
+          <t>Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5541,41 +5595,41 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="I29" t="n">
+        <v>30.375</v>
+      </c>
+      <c r="J29" t="n">
         <v>12</v>
       </c>
-      <c r="J29" t="n">
-        <v>46</v>
-      </c>
       <c r="K29" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="L29" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="M29" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="N29" t="n">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>433.36</v>
+        <v>1692.59</v>
       </c>
       <c r="Q29" t="n">
-        <v>19935</v>
+        <v>20311</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>39VRVKCF, 53SMQFHQ, 8Z6APQQC</t>
+          <t>5FPANY5G, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S29" t="b">
@@ -5585,17 +5639,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B0D3N594JW</t>
+          <t>B0H6J3YQ1D</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WRLREVELBLK</t>
+          <t>WCNVS25CBLU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Stuffcool Revel Magnetic Wireless Qi2 Certified Charger- C</t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pi</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5604,40 +5658,41 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>12</v>
       </c>
       <c r="J30" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="K30" t="n">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="L30" t="n">
-        <v>16</v>
+        <v>46</v>
+      </c>
+      <c r="M30" t="n">
+        <v>35</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>762.2</v>
+        <v>433.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>12195</v>
+        <v>19935</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>39VRVKCF, 53SMQFHQ, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S30" t="b">
@@ -5647,17 +5702,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B0CCJ8BX6C</t>
+          <t>B0D3N594JW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PBCLICKGRY</t>
+          <t>WRLREVELBLK</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Stuffcool Click 5000mAh Made in India Magnetic Wireless Po</t>
+          <t>Stuffcool Revel Magnetic Wireless Qi2 Certified Charger- C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5677,13 +5732,13 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K31" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L31" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -5692,14 +5747,14 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1185.85</v>
+        <v>762.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>11858</v>
+        <v>12195</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>6WAHMIEG</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="S31" t="b">
@@ -5709,17 +5764,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B0BXXMZLDY</t>
+          <t>B0CCJ8BX6C</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PBSP85WBLK</t>
+          <t>PBCLICKGRY</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Stuffcool Super Power 85W 20000mAh Powerbank Compatible to</t>
+          <t>Stuffcool Click 5000mAh Made in India Magnetic Wireless Po</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5739,13 +5794,13 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -5754,14 +5809,14 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2960.17</v>
+        <v>1185.85</v>
       </c>
       <c r="Q32" t="n">
-        <v>5920</v>
+        <v>11858</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>6WAHMIEG</t>
         </is>
       </c>
       <c r="S32" t="b">
@@ -5771,17 +5826,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B0H2VFTQ1C</t>
+          <t>B0BXXMZLDY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WCNUMEN45PROWHT</t>
+          <t>PBSP85WBLK</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD</t>
+          <t>Stuffcool Super Power 85W 20000mAh Powerbank Compatible to</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5790,41 +5845,40 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
-      </c>
-      <c r="I33" t="n">
-        <v>33.8</v>
+        <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="J33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>6</v>
-      </c>
-      <c r="M33" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>867.25</v>
+        <v>2960.17</v>
       </c>
       <c r="Q33" t="n">
-        <v>5204</v>
+        <v>5920</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>53SMQFHQ, 8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="S33" t="b">
@@ -5834,17 +5888,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B0GZVCYSXL</t>
+          <t>B0H2VFTQ1C</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WCNVS25CWHT</t>
+          <t>WCNUMEN45PROWHT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pi</t>
+          <t>Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5853,41 +5907,41 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="H34" t="n">
-        <v>3.666666666666667</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>15.81818181818182</v>
+        <v>33.8</v>
       </c>
       <c r="J34" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
-        <v>18.5</v>
+        <v>35</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>433.36</v>
+        <v>867.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>4334</v>
+        <v>5204</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>39VRVKCF, 5OF8HBIC</t>
+          <t>53SMQFHQ, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S34" t="b">
@@ -5897,17 +5951,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B0DFYZWRFQ</t>
+          <t>B0GZVCYSXL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PBROAM20WHT</t>
+          <t>WCNVS25CWHT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C</t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pi</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5916,41 +5970,41 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3333333333333333</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>15.81818181818182</v>
       </c>
       <c r="J35" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="K35" t="n">
-        <v>217</v>
+        <v>10</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>36</v>
+        <v>18.5</v>
       </c>
       <c r="N35" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P35" t="n">
-        <v>1067.2</v>
+        <v>433.36</v>
       </c>
       <c r="Q35" t="n">
-        <v>3202</v>
+        <v>4334</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>53SMQFHQ, 5OF8HBIC, 8Z6APQQC</t>
+          <t>39VRVKCF, 5OF8HBIC</t>
         </is>
       </c>
       <c r="S35" t="b">
@@ -5960,17 +6014,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B0DMVN35V5</t>
+          <t>B0DFYZWRFQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RMSIP16PLBLK</t>
+          <t>PBROAM20WHT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Stuffcool Rims Silicone case for iPhone 16 Plus, Magsafe E</t>
+          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5979,40 +6033,41 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I36" t="n">
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>217</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="M36" t="n">
+        <v>36</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>863.9</v>
+        <v>1067.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>1728</v>
+        <v>3202</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>53SMQFHQ, 5OF8HBIC, 8Z6APQQC</t>
         </is>
       </c>
       <c r="S36" t="b">
@@ -6022,17 +6077,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B0DB1MXGD4</t>
+          <t>B0DMVN35V5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PBCLICKMAXWHT</t>
+          <t>RMSIP16PLBLK</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stuffcool Click Max 10000mAh Powerbank with Built-in PD20W</t>
+          <t>Stuffcool Rims Silicone case for iPhone 16 Plus, Magsafe E</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6052,13 +6107,13 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -6067,14 +6122,14 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1363.81</v>
+        <v>863.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>1364</v>
+        <v>1728</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="S37" t="b">
@@ -6084,17 +6139,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B0DDTL6R6Y</t>
+          <t>B0DB1MXGD4</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PBMEGAII30WGRN</t>
+          <t>PBCLICKMAXWHT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stuffcool Mega II Compact 10,000mAh 25W Powerbank with Sam</t>
+          <t>Stuffcool Click Max 10000mAh Powerbank with Built-in PD20W</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6129,14 +6184,14 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>889.24</v>
+        <v>1363.81</v>
       </c>
       <c r="Q38" t="n">
-        <v>889</v>
+        <v>1364</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>39VRVKCF</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="S38" t="b">
@@ -6146,17 +6201,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B0C7QBPS1H</t>
+          <t>B0DDTL6R6Y</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>QUADN1BLK</t>
+          <t>PBMEGAII30WGRN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Stuffcool Quad 4 in 1 Cable 65W PD USB to Lightning, USB t</t>
+          <t>Stuffcool Mega II Compact 10,000mAh 25W Powerbank with Sam</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6191,10 +6246,10 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>296.19</v>
+        <v>889.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>296</v>
+        <v>889</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -6208,17 +6263,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B0C3GT42X5</t>
+          <t>B0C7QBPS1H</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>WCNOVA65WWHT</t>
+          <t>QUADN1BLK</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Stuffcool Nova 65W Gan Charger Made in India 3 Ports Suppo</t>
+          <t>Stuffcool Quad 4 in 1 Cable 65W PD USB to Lightning, USB t</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6227,7 +6282,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -6238,13 +6293,13 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -6253,10 +6308,15 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1270.68</v>
+        <v>296.19</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>296</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>39VRVKCF</t>
+        </is>
       </c>
       <c r="S40" t="b">
         <v>0</v>
@@ -6265,17 +6325,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B0CMTDGZSP</t>
+          <t>B0C3GT42X5</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WCNV20WHT</t>
+          <t>WCNOVA65WWHT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Nuevo PD20W Made in India Smallest Wall Charger </t>
+          <t>Stuffcool Nova 65W Gan Charger Made in India 3 Ports Suppo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6284,7 +6344,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -6310,7 +6370,7 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>304.58</v>
+        <v>1270.68</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6322,17 +6382,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B0D8443PTW</t>
+          <t>B0CMTDGZSP</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>QUADPROMAXBLK</t>
+          <t>WCNV20WHT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Stuffcool Quad Pro Max 4 in 1 Metal Braided Cable 1.5m 240</t>
+          <t xml:space="preserve">Stuffcool Nuevo PD20W Made in India Smallest Wall Charger </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6340,48 +6400,37 @@
           <t>P1-Incumbent (running down)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Quad Pro cable</t>
-        </is>
-      </c>
       <c r="G42" t="n">
-        <v>360</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>12</v>
-      </c>
-      <c r="I42" t="n">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="J42" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
-      <c r="M42" t="n">
-        <v>30</v>
-      </c>
       <c r="N42" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>508.05</v>
+        <v>304.58</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>5OF8HBIC</t>
-        </is>
       </c>
       <c r="S42" t="b">
         <v>0</v>
@@ -9739,7 +9788,7 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -9826,7 +9875,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Quad Pro cable</t>
+          <t>Quad Pro cables (coexist)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -9836,13 +9885,13 @@
         <v>360</v>
       </c>
       <c r="D4" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="E4" t="n">
-        <v>660</v>
+        <v>720</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -11571,44 +11620,44 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B0D8443PTW</t>
+          <t>B0DFYZWRFQ</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>QUADPROMAXBLK</t>
+          <t>PBROAM20WHT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuffcool Quad Pro Max 4 in 1 Metal Braided Cable 1.5m 240W Rugged e-Marker chip gold plated co</t>
+          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="J29" t="n">
-        <v>508.05</v>
+        <v>1067.2</v>
       </c>
       <c r="K29" t="n">
-        <v>36580</v>
+        <v>33083</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>46289</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="30">
@@ -11619,44 +11668,44 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B0DFYZWRFQ</t>
+          <t>B0FV2VNK12</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PBROAM20WHT</t>
+          <t>WCEMP75SIL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
+          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J30" t="n">
-        <v>1067.2</v>
+        <v>2168.95</v>
       </c>
       <c r="K30" t="n">
-        <v>33083</v>
+        <v>30365</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>46283</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="31">
@@ -11667,44 +11716,44 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B0FV2VNK12</t>
+          <t>B0DFYZWRFQ</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>WCEMP75SIL</t>
+          <t>PBROAM20WHT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuffcool Empire 75W GaN Multiport Fast Charger with 4 Type-C &amp; 1 USB-A, Smart Power Distributi</t>
+          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
         </is>
       </c>
       <c r="G31" t="n">
+        <v>23</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
         <v>20</v>
       </c>
-      <c r="H31" t="n">
-        <v>6</v>
-      </c>
-      <c r="I31" t="n">
-        <v>14</v>
-      </c>
       <c r="J31" t="n">
-        <v>2168.95</v>
+        <v>1067.2</v>
       </c>
       <c r="K31" t="n">
-        <v>30365</v>
+        <v>21344</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>46298</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="32">
@@ -11723,33 +11772,33 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B0DFYZWRFQ</t>
+          <t>B0FSSCW7WZ</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PBROAM20WHT</t>
+          <t>DUPLOBLK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuffcool Roam+ 20000mAh Compact Powerbank with 20W Type C Output Charges iPhone 50% in 30 mins</t>
+          <t>Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided Dual USB-C Connectors with Smart E-Ma</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>1067.2</v>
+        <v>698.6900000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>21344</v>
+        <v>19563</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>46289</v>
@@ -11763,44 +11812,44 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>B0FSSCW7WZ</t>
+          <t>B0H6J36G1L</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DUPLOBLK</t>
+          <t>HKNVS25CCWHT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided Dual USB-C Connectors with Smart E-Ma</t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger with Type C to C 60W 3A Cable for Samsung, Pixel &amp; i</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="H33" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>28</v>
       </c>
       <c r="J33" t="n">
-        <v>698.6900000000001</v>
+        <v>650.3099999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>19563</v>
+        <v>18209</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>46289</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="34">
@@ -11811,44 +11860,44 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B0H6J36G1L</t>
+          <t>B0H6Q2YQ9C</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HKNVS25CCWHT</t>
+          <t>PBOMNIPROSIL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger with Type C to C 60W 3A Cable for Samsung, Pixel &amp; i</t>
+          <t>Stuffcool Omni Pro Qi2.2 Certified 25W MagSafe Powerbank 10000mAh with Apple Watch Charger, 35W</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I34" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
-        <v>650.3099999999999</v>
+        <v>3134.97</v>
       </c>
       <c r="K34" t="n">
-        <v>18209</v>
+        <v>15675</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="35">
@@ -11859,44 +11908,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B0H6Q2YQ9C</t>
+          <t>B0H5HYK4KZ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PBOMNIPROSIL</t>
+          <t>PBOMNIIVRY</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuffcool Omni Pro Qi2.2 Certified 25W MagSafe Powerbank 10000mAh with Apple Watch Charger, 35W</t>
+          <t xml:space="preserve">Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank with Dedicated Apple Watch Charging </t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="H35" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J35" t="n">
-        <v>3134.97</v>
+        <v>1692.59</v>
       </c>
       <c r="K35" t="n">
-        <v>15675</v>
+        <v>15233</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>46290</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="36">
@@ -11907,44 +11956,44 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B0H5HYK4KZ</t>
+          <t>B0H552PBFY</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PBOMNIIVRY</t>
+          <t>HKNVS25CCORG</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Omni 3-in-1 10000mAh Magnetic Wireless Powerbank with Dedicated Apple Watch Charging </t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger with Type C to C 60W 3A Cable for Samsung, Pixel &amp; i</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>1692.59</v>
+        <v>650.3099999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>15233</v>
+        <v>13006</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>46298</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="37">
@@ -11963,33 +12012,33 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>B0H552PBFY</t>
+          <t>B0FSSCW7WZ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HKNVS25CCORG</t>
+          <t>DUPLOBLK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger with Type C to C 60W 3A Cable for Samsung, Pixel &amp; i</t>
+          <t>Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided Dual USB-C Connectors with Smart E-Ma</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>650.3099999999999</v>
+        <v>698.6900000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>13006</v>
+        <v>11179</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>46283</v>
@@ -12003,44 +12052,44 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>B0FSSCW7WZ</t>
+          <t>B0GN99CJ8F</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DUPLOBLK</t>
+          <t>WCZENO100WWHT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuffcool Duplo 140W Dual Type-C Cable 1.2m Nylon-Braided Dual USB-C Connectors with Smart E-Ma</t>
+          <t xml:space="preserve">Stuffcool Zeno 100W Desktop Charging Station, 65W Retractable Type-C Cable, Dual 100W PD 3.0 &amp; </t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J38" t="n">
-        <v>698.6900000000001</v>
+        <v>2168.95</v>
       </c>
       <c r="K38" t="n">
-        <v>11179</v>
+        <v>10845</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>46283</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="39">
@@ -12051,44 +12100,44 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>39VRVKCF</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B0GN99CJ8F</t>
+          <t>B0H6J3YQ1D</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>WCZENO100WWHT</t>
+          <t>WCNVS25CBLU</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Zeno 100W Desktop Charging Station, 65W Retractable Type-C Cable, Dual 100W PD 3.0 &amp; </t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pixel &amp; iPhone Blue</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>2168.95</v>
+        <v>433.36</v>
       </c>
       <c r="K39" t="n">
-        <v>10845</v>
+        <v>10401</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>46298</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="40">
@@ -12099,44 +12148,44 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>39VRVKCF</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>B0H6J3YQ1D</t>
+          <t>B0H2VFTQ1C</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>WCNVS25CBLU</t>
+          <t>WCNUMEN45PROWHT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger for Samsung, Pixel &amp; iPhone Blue</t>
+          <t xml:space="preserve">Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD PPS Fast Charging, Supports Samsung </t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="H40" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>433.36</v>
+        <v>867.25</v>
       </c>
       <c r="K40" t="n">
-        <v>10401</v>
+        <v>8672</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>46270</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="41">
@@ -12147,44 +12196,44 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>39VRVKCF</t>
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>B0H2VFTQ1C</t>
+          <t>B0DPHR4FG7</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WCNUMEN45PROWHT</t>
+          <t>PBLUCIDWHT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuffcool Numen 45 Pro Dual Type-C GaN Charger with 45W PD PPS Fast Charging, Supports Samsung </t>
+          <t>Stuffcool Lucid 15W Smallest Magnetic Wireless Powerbank 5000Mah Battery Capacity for iPhone 16</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J41" t="n">
-        <v>867.25</v>
+        <v>942.96</v>
       </c>
       <c r="K41" t="n">
-        <v>8672</v>
+        <v>8487</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>46283</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="42">
@@ -12195,44 +12244,44 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>39VRVKCF</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>B0DPHR4FG7</t>
+          <t>B0GZBJRKSM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PBLUCIDWHT</t>
+          <t>PRIMUS1BLK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuffcool Lucid 15W Smallest Magnetic Wireless Powerbank 5000Mah Battery Capacity for iPhone 16</t>
+          <t>Stuffcool Primus USB 4 Type-C to Type-C Cable with 240W Power and 40Gbps Data with 8K Video Tra</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H42" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J42" t="n">
-        <v>942.96</v>
+        <v>605.3</v>
       </c>
       <c r="K42" t="n">
-        <v>8487</v>
+        <v>8474</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>46270</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="43">
@@ -12243,11 +12292,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5OF8HBIC</t>
+          <t>8Z6APQQC</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -12265,22 +12314,22 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J43" t="n">
         <v>605.3</v>
       </c>
       <c r="K43" t="n">
-        <v>8474</v>
+        <v>7264</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="44">
@@ -12291,44 +12340,44 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8Z6APQQC</t>
+          <t>5OF8HBIC</t>
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B0GZBJRKSM</t>
+          <t>B0H552PBFY</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PRIMUS1BLK</t>
+          <t>HKNVS25CCORG</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuffcool Primus USB 4 Type-C to Type-C Cable with 240W Power and 40Gbps Data with 8K Video Tra</t>
+          <t>Stuffcool Novus 25W Super Fast GaN Charger with Type C to C 60W 3A Cable for Samsung, Pixel &amp; i</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J44" t="n">
-        <v>605.3</v>
+        <v>650.3099999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>7264</v>
+        <v>6503</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="45">
@@ -12395,33 +12444,33 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>B0H552PBFY</t>
+          <t>B0D8443PTW</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HKNVS25CCORG</t>
+          <t>QUADPROMAXBLK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuffcool Novus 25W Super Fast GaN Charger with Type C to C 60W 3A Cable for Samsung, Pixel &amp; i</t>
+          <t>Stuffcool Quad Pro Max 4 in 1 Metal Braided Cable 1.5m 240W Rugged e-Marker chip gold plated co</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J46" t="n">
-        <v>650.3099999999999</v>
+        <v>508.05</v>
       </c>
       <c r="K46" t="n">
-        <v>6503</v>
+        <v>6097</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>46289</v>
@@ -12867,11 +12916,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>39VRVKCF</t>
+          <t>53SMQFHQ</t>
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -12904,7 +12953,7 @@
         <v>2076</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>46270</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="57">
@@ -12915,11 +12964,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>53SMQFHQ</t>
+          <t>39VRVKCF</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -12952,7 +13001,7 @@
         <v>2076</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>46283</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="58">
@@ -13011,20 +13060,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>39VRVKCF</t>
+          <t>5FPANY5G</t>
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>46237</v>
+        <v>46265</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B0H54Z8RSJ</t>
+          <t>B0H552PBFY</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HKNVS25CCBLU</t>
+          <t>HKNVS25CCORG</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -13048,7 +13097,7 @@
         <v>1301</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>46270</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="60">
@@ -13059,20 +13108,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5FPANY5G</t>
+          <t>39VRVKCF</t>
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>46265</v>
+        <v>46237</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0H552PBFY</t>
+          <t>B0H54Z8RSJ</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>HKNVS25CCORG</t>
+          <t>HKNVS25CCBLU</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -13096,7 +13145,7 @@
         <v>1301</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>46298</v>
+        <v>46270</v>
       </c>
     </row>
   </sheetData>
